--- a/cơ sinh/whack-a-mole-hand-control/src/game_angles_summary.xlsx
+++ b/cơ sinh/whack-a-mole-hand-control/src/game_angles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3336,6 +3336,489 @@
         <v>-5512.6</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-10-24T21:14:22.248953</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>210</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>17</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>99</v>
+      </c>
+      <c r="U41" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-10-24T21:17:34.641117</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>nd</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>760</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L42" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>475</v>
+      </c>
+      <c r="U42" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-10-24T21:31:00.408943</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>dc</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>479</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>353</v>
+      </c>
+      <c r="U43" t="n">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-10-24T21:31:38.776984</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fv</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>901</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>887</v>
+      </c>
+      <c r="U44" t="n">
+        <v>98.40000000000001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-10-24T21:32:29.134490</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>902</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I45" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="L45" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>13</v>
+      </c>
+      <c r="O45" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>641</v>
+      </c>
+      <c r="U45" t="n">
+        <v>71.09999999999999</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-10-25T09:22:03.268434</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>aa</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>175</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F46" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I46" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L46" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>8</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-10-27T09:47:05.662691</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nn</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>70</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I47" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
